--- a/artfynd/A 63149-2025 artfynd.xlsx
+++ b/artfynd/A 63149-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,6 +769,3102 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133906074</v>
+      </c>
+      <c r="B3" t="n">
+        <v>110101</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>716847</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6367896</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikt spridd.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133906050</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99116</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>716781</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6367774</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133906041</v>
+      </c>
+      <c r="B5" t="n">
+        <v>110101</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>716731</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6367719</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133906113</v>
+      </c>
+      <c r="B6" t="n">
+        <v>110101</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>716867</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6367982</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133906087</v>
+      </c>
+      <c r="B7" t="n">
+        <v>110101</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>716824</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6367939</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133905920</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>716715</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6367553</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133906080</v>
+      </c>
+      <c r="B9" t="n">
+        <v>110101</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>716847</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6367921</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133905919</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>716736</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6367574</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosök vid basen av död gran.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133905926</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58681</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26, A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>716777</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6367814</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Skog röjd på en och små lövträd.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133906030</v>
+      </c>
+      <c r="B12" t="n">
+        <v>110101</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>716719</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6367706</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133906008</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99167</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>716736</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6367574</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133906108</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99167</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>716880</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6367998</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133906043</v>
+      </c>
+      <c r="B15" t="n">
+        <v>110101</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>716740</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6367726</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133906090</v>
+      </c>
+      <c r="B16" t="n">
+        <v>110101</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>716837</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6367949</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133906106</v>
+      </c>
+      <c r="B17" t="n">
+        <v>110101</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>716891</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6367995</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133906102</v>
+      </c>
+      <c r="B18" t="n">
+        <v>110101</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>716870</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6367996</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133906077</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99167</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>716854</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6367916</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133906072</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99167</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 körväg, A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>716824</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6367869</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>133906001</v>
+      </c>
+      <c r="B21" t="n">
+        <v>110101</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>716693</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6367557</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>133906092</v>
+      </c>
+      <c r="B22" t="n">
+        <v>110101</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>716848</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6367955</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>133906094</v>
+      </c>
+      <c r="B23" t="n">
+        <v>110101</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>716858</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6367961</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>133906078</v>
+      </c>
+      <c r="B24" t="n">
+        <v>110101</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>716854</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6367916</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>133906111</v>
+      </c>
+      <c r="B25" t="n">
+        <v>110101</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>716880</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6367991</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>133906016</v>
+      </c>
+      <c r="B26" t="n">
+        <v>110101</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>716764</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6367627</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>133906096</v>
+      </c>
+      <c r="B27" t="n">
+        <v>110101</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>716857</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6367975</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>133906116</v>
+      </c>
+      <c r="B28" t="n">
+        <v>110101</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>716870</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6367944</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Skogen buskröjd inför avverkning. Mellanskog.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>133906105</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99167</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>219864</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Orchis mascula</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>716891</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6367995</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>133906109</v>
+      </c>
+      <c r="B30" t="n">
+        <v>110101</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>716880</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6367998</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>133906034</v>
+      </c>
+      <c r="B31" t="n">
+        <v>110101</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>716743</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6367714</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63149-2025 artfynd.xlsx
+++ b/artfynd/A 63149-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>133906074</v>
       </c>
       <c r="B3" t="n">
-        <v>110101</v>
+        <v>110103</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>133906050</v>
       </c>
       <c r="B4" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>133906041</v>
       </c>
       <c r="B5" t="n">
-        <v>110101</v>
+        <v>110103</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>133906113</v>
       </c>
       <c r="B6" t="n">
-        <v>110101</v>
+        <v>110103</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133906087</v>
+        <v>133905920</v>
       </c>
       <c r="B7" t="n">
-        <v>110101</v>
+        <v>57955</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,37 +1215,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716824</v>
+        <v>716715</v>
       </c>
       <c r="R7" t="n">
-        <v>6367939</v>
+        <v>6367553</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,11 +1290,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1306,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133905920</v>
+        <v>133906087</v>
       </c>
       <c r="B8" t="n">
-        <v>57955</v>
+        <v>110103</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1317,42 +1317,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716715</v>
+        <v>716824</v>
       </c>
       <c r="R8" t="n">
-        <v>6367553</v>
+        <v>6367939</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1392,6 +1387,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133906080</v>
+        <v>133905919</v>
       </c>
       <c r="B9" t="n">
-        <v>110101</v>
+        <v>57955</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,34 +1419,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716847</v>
+        <v>716736</v>
       </c>
       <c r="R9" t="n">
-        <v>6367921</v>
+        <v>6367574</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1481,6 +1486,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosök vid basen av död gran.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1489,11 +1499,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1510,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133905919</v>
+        <v>133906080</v>
       </c>
       <c r="B10" t="n">
-        <v>57955</v>
+        <v>110103</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1521,39 +1526,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716736</v>
+        <v>716847</v>
       </c>
       <c r="R10" t="n">
-        <v>6367574</v>
+        <v>6367921</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1588,11 +1588,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Födosök vid basen av död gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1601,6 +1596,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1741,7 +1741,7 @@
         <v>133906030</v>
       </c>
       <c r="B12" t="n">
-        <v>110101</v>
+        <v>110103</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>133906008</v>
       </c>
       <c r="B13" t="n">
-        <v>99167</v>
+        <v>99169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>133906108</v>
       </c>
       <c r="B14" t="n">
-        <v>99167</v>
+        <v>99169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>133906043</v>
       </c>
       <c r="B15" t="n">
-        <v>110101</v>
+        <v>110103</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>133906090</v>
       </c>
       <c r="B16" t="n">
-        <v>110101</v>
+        <v>110103</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>133906106</v>
       </c>
       <c r="B17" t="n">
-        <v>110101</v>
+        <v>110103</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>133906102</v>
       </c>
       <c r="B18" t="n">
-        <v>110101</v>
+        <v>110103</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>133906077</v>
       </c>
       <c r="B19" t="n">
-        <v>99167</v>
+        <v>99169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>133906072</v>
       </c>
       <c r="B20" t="n">
-        <v>99167</v>
+        <v>99169</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>133906001</v>
       </c>
       <c r="B21" t="n">
-        <v>110101</v>
+        <v>110103</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>133906092</v>
       </c>
       <c r="B22" t="n">
-        <v>110101</v>
+        <v>110103</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>133906094</v>
       </c>
       <c r="B23" t="n">
-        <v>110101</v>
+        <v>110103</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>133906078</v>
       </c>
       <c r="B24" t="n">
-        <v>110101</v>
+        <v>110103</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>133906111</v>
       </c>
       <c r="B25" t="n">
-        <v>110101</v>
+        <v>110103</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>133906016</v>
       </c>
       <c r="B26" t="n">
-        <v>110101</v>
+        <v>110103</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>133906096</v>
       </c>
       <c r="B27" t="n">
-        <v>110101</v>
+        <v>110103</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>133906116</v>
       </c>
       <c r="B28" t="n">
-        <v>110101</v>
+        <v>110103</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>133906105</v>
       </c>
       <c r="B29" t="n">
-        <v>99167</v>
+        <v>99169</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>133906109</v>
       </c>
       <c r="B30" t="n">
-        <v>110101</v>
+        <v>110103</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>133906034</v>
       </c>
       <c r="B31" t="n">
-        <v>110101</v>
+        <v>110103</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 63149-2025 artfynd.xlsx
+++ b/artfynd/A 63149-2025 artfynd.xlsx
@@ -2373,27 +2373,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133906102</v>
+        <v>133906077</v>
       </c>
       <c r="B18" t="n">
-        <v>110103</v>
+        <v>99169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2401,17 +2401,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716870</v>
+        <v>716854</v>
       </c>
       <c r="R18" t="n">
-        <v>6367996</v>
+        <v>6367916</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2444,11 +2453,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2480,27 +2484,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133906077</v>
+        <v>133906102</v>
       </c>
       <c r="B19" t="n">
-        <v>99169</v>
+        <v>110103</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2508,26 +2512,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716854</v>
+        <v>716870</v>
       </c>
       <c r="R19" t="n">
-        <v>6367916</v>
+        <v>6367996</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2560,6 +2555,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 63149-2025 artfynd.xlsx
+++ b/artfynd/A 63149-2025 artfynd.xlsx
@@ -1204,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133905920</v>
+        <v>133906087</v>
       </c>
       <c r="B7" t="n">
-        <v>57955</v>
+        <v>110103</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,42 +1215,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716715</v>
+        <v>716824</v>
       </c>
       <c r="R7" t="n">
-        <v>6367553</v>
+        <v>6367939</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,6 +1285,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1306,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133906087</v>
+        <v>133905920</v>
       </c>
       <c r="B8" t="n">
-        <v>110103</v>
+        <v>57955</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1317,37 +1317,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716824</v>
+        <v>716715</v>
       </c>
       <c r="R8" t="n">
-        <v>6367939</v>
+        <v>6367553</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,11 +1392,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">

--- a/artfynd/A 63149-2025 artfynd.xlsx
+++ b/artfynd/A 63149-2025 artfynd.xlsx
@@ -1204,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133906087</v>
+        <v>133905920</v>
       </c>
       <c r="B7" t="n">
-        <v>110103</v>
+        <v>57955</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,37 +1215,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716824</v>
+        <v>716715</v>
       </c>
       <c r="R7" t="n">
-        <v>6367939</v>
+        <v>6367553</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,11 +1290,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1306,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133905920</v>
+        <v>133906087</v>
       </c>
       <c r="B8" t="n">
-        <v>57955</v>
+        <v>110103</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1317,42 +1317,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716715</v>
+        <v>716824</v>
       </c>
       <c r="R8" t="n">
-        <v>6367553</v>
+        <v>6367939</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1392,6 +1387,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -2373,27 +2373,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133906077</v>
+        <v>133906102</v>
       </c>
       <c r="B18" t="n">
-        <v>99169</v>
+        <v>110103</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2401,26 +2401,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716854</v>
+        <v>716870</v>
       </c>
       <c r="R18" t="n">
-        <v>6367916</v>
+        <v>6367996</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2453,6 +2444,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,27 +2480,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133906102</v>
+        <v>133906077</v>
       </c>
       <c r="B19" t="n">
-        <v>110103</v>
+        <v>99169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2512,17 +2508,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716870</v>
+        <v>716854</v>
       </c>
       <c r="R19" t="n">
-        <v>6367996</v>
+        <v>6367916</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2555,11 +2560,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 63149-2025 artfynd.xlsx
+++ b/artfynd/A 63149-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>133906074</v>
       </c>
       <c r="B3" t="n">
-        <v>110103</v>
+        <v>110131</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>133906050</v>
       </c>
       <c r="B4" t="n">
-        <v>99118</v>
+        <v>99146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>133906041</v>
       </c>
       <c r="B5" t="n">
-        <v>110103</v>
+        <v>110131</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>133906113</v>
       </c>
       <c r="B6" t="n">
-        <v>110103</v>
+        <v>110131</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>133905920</v>
       </c>
       <c r="B7" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>133906087</v>
       </c>
       <c r="B8" t="n">
-        <v>110103</v>
+        <v>110131</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>133905919</v>
       </c>
       <c r="B9" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>133906080</v>
       </c>
       <c r="B10" t="n">
-        <v>110103</v>
+        <v>110131</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,10 +1617,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133905926</v>
+        <v>133906030</v>
       </c>
       <c r="B11" t="n">
-        <v>58681</v>
+        <v>110131</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1628,56 +1628,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103055</v>
+        <v>220299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716777</v>
+        <v>716719</v>
       </c>
       <c r="R11" t="n">
-        <v>6367814</v>
+        <v>6367706</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1709,11 +1690,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Skog röjd på en och små lövträd.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1722,6 +1698,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1738,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133906030</v>
+        <v>133905926</v>
       </c>
       <c r="B12" t="n">
-        <v>110103</v>
+        <v>58688</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,37 +1730,56 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>103055</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716719</v>
+        <v>716777</v>
       </c>
       <c r="R12" t="n">
-        <v>6367706</v>
+        <v>6367814</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1811,6 +1811,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Skog röjd på en och små lövträd.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1819,11 +1824,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1843,7 +1843,7 @@
         <v>133906008</v>
       </c>
       <c r="B13" t="n">
-        <v>99169</v>
+        <v>99197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>133906108</v>
       </c>
       <c r="B14" t="n">
-        <v>99169</v>
+        <v>99197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>133906043</v>
       </c>
       <c r="B15" t="n">
-        <v>110103</v>
+        <v>110131</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>133906090</v>
       </c>
       <c r="B16" t="n">
-        <v>110103</v>
+        <v>110131</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>133906106</v>
       </c>
       <c r="B17" t="n">
-        <v>110103</v>
+        <v>110131</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>133906102</v>
       </c>
       <c r="B18" t="n">
-        <v>110103</v>
+        <v>110131</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>133906077</v>
       </c>
       <c r="B19" t="n">
-        <v>99169</v>
+        <v>99197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>133906072</v>
       </c>
       <c r="B20" t="n">
-        <v>99169</v>
+        <v>99197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>133906001</v>
       </c>
       <c r="B21" t="n">
-        <v>110103</v>
+        <v>110131</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>133906092</v>
       </c>
       <c r="B22" t="n">
-        <v>110103</v>
+        <v>110131</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>133906094</v>
       </c>
       <c r="B23" t="n">
-        <v>110103</v>
+        <v>110131</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>133906078</v>
       </c>
       <c r="B24" t="n">
-        <v>110103</v>
+        <v>110131</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>133906111</v>
       </c>
       <c r="B25" t="n">
-        <v>110103</v>
+        <v>110131</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3232,10 +3232,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133906016</v>
+        <v>133906096</v>
       </c>
       <c r="B26" t="n">
-        <v>110103</v>
+        <v>110131</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3263,14 +3263,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716764</v>
+        <v>716857</v>
       </c>
       <c r="R26" t="n">
-        <v>6367627</v>
+        <v>6367975</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3305,6 +3305,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3316,7 +3321,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3334,10 +3339,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133906096</v>
+        <v>133906016</v>
       </c>
       <c r="B27" t="n">
-        <v>110103</v>
+        <v>110131</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3365,14 +3370,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>716857</v>
+        <v>716764</v>
       </c>
       <c r="R27" t="n">
-        <v>6367975</v>
+        <v>6367627</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3407,11 +3412,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3444,7 +3444,7 @@
         <v>133906116</v>
       </c>
       <c r="B28" t="n">
-        <v>110103</v>
+        <v>110131</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>133906105</v>
       </c>
       <c r="B29" t="n">
-        <v>99169</v>
+        <v>99197</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>133906109</v>
       </c>
       <c r="B30" t="n">
-        <v>110103</v>
+        <v>110131</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>133906034</v>
       </c>
       <c r="B31" t="n">
-        <v>110103</v>
+        <v>110131</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 63149-2025 artfynd.xlsx
+++ b/artfynd/A 63149-2025 artfynd.xlsx
@@ -879,59 +879,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133906050</v>
+        <v>133906041</v>
       </c>
       <c r="B4" t="n">
-        <v>99146</v>
+        <v>110131</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716781</v>
+        <v>716731</v>
       </c>
       <c r="R4" t="n">
-        <v>6367774</v>
+        <v>6367719</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,45 +981,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133906041</v>
+        <v>133906050</v>
       </c>
       <c r="B5" t="n">
-        <v>110131</v>
+        <v>99146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716731</v>
+        <v>716781</v>
       </c>
       <c r="R5" t="n">
-        <v>6367719</v>
+        <v>6367774</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133905919</v>
+        <v>133906080</v>
       </c>
       <c r="B9" t="n">
-        <v>57962</v>
+        <v>110131</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,39 +1419,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716736</v>
+        <v>716847</v>
       </c>
       <c r="R9" t="n">
-        <v>6367574</v>
+        <v>6367921</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1486,11 +1481,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosök vid basen av död gran.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1499,6 +1489,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1515,10 +1510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133906080</v>
+        <v>133905919</v>
       </c>
       <c r="B10" t="n">
-        <v>110131</v>
+        <v>57962</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,34 +1521,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716847</v>
+        <v>716736</v>
       </c>
       <c r="R10" t="n">
-        <v>6367921</v>
+        <v>6367574</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1588,6 +1588,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosök vid basen av död gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1596,11 +1601,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1617,10 +1617,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133906030</v>
+        <v>133905926</v>
       </c>
       <c r="B11" t="n">
-        <v>110131</v>
+        <v>58688</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1628,37 +1628,56 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220299</v>
+        <v>103055</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716719</v>
+        <v>716777</v>
       </c>
       <c r="R11" t="n">
-        <v>6367706</v>
+        <v>6367814</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1690,6 +1709,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Skog röjd på en och små lövträd.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1698,11 +1722,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1719,10 +1738,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133905926</v>
+        <v>133906030</v>
       </c>
       <c r="B12" t="n">
-        <v>58688</v>
+        <v>110131</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,56 +1749,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103055</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716777</v>
+        <v>716719</v>
       </c>
       <c r="R12" t="n">
-        <v>6367814</v>
+        <v>6367706</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1811,11 +1811,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Skog röjd på en och små lövträd.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1824,6 +1819,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1840,7 +1840,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133906008</v>
+        <v>133906108</v>
       </c>
       <c r="B13" t="n">
         <v>99197</v>
@@ -1880,14 +1880,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716736</v>
+        <v>716880</v>
       </c>
       <c r="R13" t="n">
-        <v>6367574</v>
+        <v>6367998</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1951,27 +1951,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133906108</v>
+        <v>133906090</v>
       </c>
       <c r="B14" t="n">
-        <v>99197</v>
+        <v>110131</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1979,26 +1979,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716880</v>
+        <v>716837</v>
       </c>
       <c r="R14" t="n">
-        <v>6367998</v>
+        <v>6367949</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2062,27 +2053,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133906043</v>
+        <v>133906008</v>
       </c>
       <c r="B15" t="n">
-        <v>110131</v>
+        <v>99197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2090,17 +2081,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716740</v>
+        <v>716736</v>
       </c>
       <c r="R15" t="n">
-        <v>6367726</v>
+        <v>6367574</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133906090</v>
+        <v>133906043</v>
       </c>
       <c r="B16" t="n">
         <v>110131</v>
@@ -2195,14 +2195,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716837</v>
+        <v>716740</v>
       </c>
       <c r="R16" t="n">
-        <v>6367949</v>
+        <v>6367726</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2702,7 +2702,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133906001</v>
+        <v>133906092</v>
       </c>
       <c r="B21" t="n">
         <v>110131</v>
@@ -2733,14 +2733,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716693</v>
+        <v>716848</v>
       </c>
       <c r="R21" t="n">
-        <v>6367557</v>
+        <v>6367955</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2775,6 +2775,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2786,7 +2791,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2804,7 +2809,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133906092</v>
+        <v>133906001</v>
       </c>
       <c r="B22" t="n">
         <v>110131</v>
@@ -2835,14 +2840,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>716848</v>
+        <v>716693</v>
       </c>
       <c r="R22" t="n">
-        <v>6367955</v>
+        <v>6367557</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2877,11 +2882,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3659,7 +3659,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133906109</v>
+        <v>133906034</v>
       </c>
       <c r="B30" t="n">
         <v>110131</v>
@@ -3690,14 +3690,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>716880</v>
+        <v>716743</v>
       </c>
       <c r="R30" t="n">
-        <v>6367998</v>
+        <v>6367714</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3732,11 +3732,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3748,7 +3743,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3766,7 +3761,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133906034</v>
+        <v>133906109</v>
       </c>
       <c r="B31" t="n">
         <v>110131</v>
@@ -3797,14 +3792,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>716743</v>
+        <v>716880</v>
       </c>
       <c r="R31" t="n">
-        <v>6367714</v>
+        <v>6367998</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3839,6 +3834,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>

--- a/artfynd/A 63149-2025 artfynd.xlsx
+++ b/artfynd/A 63149-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>133906074</v>
       </c>
       <c r="B3" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>133906041</v>
       </c>
       <c r="B4" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>133906050</v>
       </c>
       <c r="B5" t="n">
-        <v>99146</v>
+        <v>99156</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>133906113</v>
       </c>
       <c r="B6" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>133905920</v>
       </c>
       <c r="B7" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>133906087</v>
       </c>
       <c r="B8" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>133906080</v>
       </c>
       <c r="B9" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>133905919</v>
       </c>
       <c r="B10" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,10 +1617,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133905926</v>
+        <v>133906030</v>
       </c>
       <c r="B11" t="n">
-        <v>58688</v>
+        <v>110141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1628,56 +1628,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103055</v>
+        <v>220299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716777</v>
+        <v>716719</v>
       </c>
       <c r="R11" t="n">
-        <v>6367814</v>
+        <v>6367706</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1709,11 +1690,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Skog röjd på en och små lövträd.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1722,6 +1698,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1738,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133906030</v>
+        <v>133905926</v>
       </c>
       <c r="B12" t="n">
-        <v>110131</v>
+        <v>58698</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,37 +1730,56 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>103055</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716719</v>
+        <v>716777</v>
       </c>
       <c r="R12" t="n">
-        <v>6367706</v>
+        <v>6367814</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1811,6 +1811,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Skog röjd på en och små lövträd.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1819,11 +1824,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1843,7 +1843,7 @@
         <v>133906108</v>
       </c>
       <c r="B13" t="n">
-        <v>99197</v>
+        <v>99207</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>133906090</v>
       </c>
       <c r="B14" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>133906008</v>
       </c>
       <c r="B15" t="n">
-        <v>99197</v>
+        <v>99207</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>133906043</v>
       </c>
       <c r="B16" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>133906106</v>
       </c>
       <c r="B17" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2373,27 +2373,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133906102</v>
+        <v>133906077</v>
       </c>
       <c r="B18" t="n">
-        <v>110131</v>
+        <v>99207</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2401,17 +2401,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716870</v>
+        <v>716854</v>
       </c>
       <c r="R18" t="n">
-        <v>6367996</v>
+        <v>6367916</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2444,11 +2453,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2480,27 +2484,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133906077</v>
+        <v>133906102</v>
       </c>
       <c r="B19" t="n">
-        <v>99197</v>
+        <v>110141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2508,26 +2512,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716854</v>
+        <v>716870</v>
       </c>
       <c r="R19" t="n">
-        <v>6367916</v>
+        <v>6367996</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2560,6 +2555,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,7 +2594,7 @@
         <v>133906072</v>
       </c>
       <c r="B20" t="n">
-        <v>99197</v>
+        <v>99207</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>133906092</v>
       </c>
       <c r="B21" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>133906001</v>
       </c>
       <c r="B22" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>133906094</v>
       </c>
       <c r="B23" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>133906078</v>
       </c>
       <c r="B24" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>133906111</v>
       </c>
       <c r="B25" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>133906096</v>
       </c>
       <c r="B26" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>133906016</v>
       </c>
       <c r="B27" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3441,27 +3441,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133906116</v>
+        <v>133906105</v>
       </c>
       <c r="B28" t="n">
-        <v>110131</v>
+        <v>99207</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3469,20 +3469,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>716870</v>
+        <v>716891</v>
       </c>
       <c r="R28" t="n">
-        <v>6367944</v>
+        <v>6367995</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3512,11 +3521,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Skogen buskröjd inför avverkning. Mellanskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3548,27 +3552,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133906105</v>
+        <v>133906116</v>
       </c>
       <c r="B29" t="n">
-        <v>99197</v>
+        <v>110141</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3576,29 +3580,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>716891</v>
+        <v>716870</v>
       </c>
       <c r="R29" t="n">
-        <v>6367995</v>
+        <v>6367944</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3628,6 +3623,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Skogen buskröjd inför avverkning. Mellanskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3659,10 +3659,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133906034</v>
+        <v>133906109</v>
       </c>
       <c r="B30" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3690,14 +3690,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>716743</v>
+        <v>716880</v>
       </c>
       <c r="R30" t="n">
-        <v>6367714</v>
+        <v>6367998</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3732,6 +3732,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3743,7 +3748,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3761,10 +3766,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133906109</v>
+        <v>133906034</v>
       </c>
       <c r="B31" t="n">
-        <v>110131</v>
+        <v>110141</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3792,14 +3797,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>716880</v>
+        <v>716743</v>
       </c>
       <c r="R31" t="n">
-        <v>6367998</v>
+        <v>6367714</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3834,11 +3839,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>

--- a/artfynd/A 63149-2025 artfynd.xlsx
+++ b/artfynd/A 63149-2025 artfynd.xlsx
@@ -879,45 +879,59 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133906041</v>
+        <v>133906050</v>
       </c>
       <c r="B4" t="n">
-        <v>110141</v>
+        <v>99156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716731</v>
+        <v>716781</v>
       </c>
       <c r="R4" t="n">
-        <v>6367719</v>
+        <v>6367774</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,59 +995,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133906050</v>
+        <v>133906041</v>
       </c>
       <c r="B5" t="n">
-        <v>99156</v>
+        <v>110141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716781</v>
+        <v>716731</v>
       </c>
       <c r="R5" t="n">
-        <v>6367774</v>
+        <v>6367719</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133906080</v>
+        <v>133905919</v>
       </c>
       <c r="B9" t="n">
-        <v>110141</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,34 +1419,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716847</v>
+        <v>716736</v>
       </c>
       <c r="R9" t="n">
-        <v>6367921</v>
+        <v>6367574</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1481,6 +1486,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Födosök vid basen av död gran.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1489,11 +1499,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1510,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133905919</v>
+        <v>133906080</v>
       </c>
       <c r="B10" t="n">
-        <v>57972</v>
+        <v>110141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1521,39 +1526,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716736</v>
+        <v>716847</v>
       </c>
       <c r="R10" t="n">
-        <v>6367574</v>
+        <v>6367921</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1588,11 +1588,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Födosök vid basen av död gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1601,6 +1596,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1840,7 +1840,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133906108</v>
+        <v>133906008</v>
       </c>
       <c r="B13" t="n">
         <v>99207</v>
@@ -1880,14 +1880,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716880</v>
+        <v>716736</v>
       </c>
       <c r="R13" t="n">
-        <v>6367998</v>
+        <v>6367574</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1951,27 +1951,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133906090</v>
+        <v>133906108</v>
       </c>
       <c r="B14" t="n">
-        <v>110141</v>
+        <v>99207</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1979,17 +1979,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716837</v>
+        <v>716880</v>
       </c>
       <c r="R14" t="n">
-        <v>6367949</v>
+        <v>6367998</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2053,27 +2062,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133906008</v>
+        <v>133906090</v>
       </c>
       <c r="B15" t="n">
-        <v>99207</v>
+        <v>110141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2081,26 +2090,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716736</v>
+        <v>716837</v>
       </c>
       <c r="R15" t="n">
-        <v>6367574</v>
+        <v>6367949</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2373,27 +2373,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133906077</v>
+        <v>133906102</v>
       </c>
       <c r="B18" t="n">
-        <v>99207</v>
+        <v>110141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2401,26 +2401,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716854</v>
+        <v>716870</v>
       </c>
       <c r="R18" t="n">
-        <v>6367916</v>
+        <v>6367996</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2453,6 +2444,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,27 +2480,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133906102</v>
+        <v>133906077</v>
       </c>
       <c r="B19" t="n">
-        <v>110141</v>
+        <v>99207</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2512,17 +2508,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716870</v>
+        <v>716854</v>
       </c>
       <c r="R19" t="n">
-        <v>6367996</v>
+        <v>6367916</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2555,11 +2560,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3441,27 +3441,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133906105</v>
+        <v>133906116</v>
       </c>
       <c r="B28" t="n">
-        <v>99207</v>
+        <v>110141</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3469,29 +3469,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>716891</v>
+        <v>716870</v>
       </c>
       <c r="R28" t="n">
-        <v>6367995</v>
+        <v>6367944</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3521,6 +3512,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Skogen buskröjd inför avverkning. Mellanskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3552,27 +3548,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133906116</v>
+        <v>133906105</v>
       </c>
       <c r="B29" t="n">
-        <v>110141</v>
+        <v>99207</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3580,20 +3576,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>716870</v>
+        <v>716891</v>
       </c>
       <c r="R29" t="n">
-        <v>6367944</v>
+        <v>6367995</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3623,11 +3628,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Skogen buskröjd inför avverkning. Mellanskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 63149-2025 artfynd.xlsx
+++ b/artfynd/A 63149-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>133906074</v>
       </c>
       <c r="B3" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>133906041</v>
       </c>
       <c r="B5" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>133906113</v>
       </c>
       <c r="B6" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>133906087</v>
       </c>
       <c r="B8" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>133906080</v>
       </c>
       <c r="B10" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,10 +1617,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133906030</v>
+        <v>133905926</v>
       </c>
       <c r="B11" t="n">
-        <v>110141</v>
+        <v>58698</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1628,37 +1628,56 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220299</v>
+        <v>103055</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716719</v>
+        <v>716777</v>
       </c>
       <c r="R11" t="n">
-        <v>6367706</v>
+        <v>6367814</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1690,6 +1709,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Skog röjd på en och små lövträd.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1698,11 +1722,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1719,10 +1738,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133905926</v>
+        <v>133906030</v>
       </c>
       <c r="B12" t="n">
-        <v>58698</v>
+        <v>110142</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,56 +1749,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103055</v>
+        <v>220299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716777</v>
+        <v>716719</v>
       </c>
       <c r="R12" t="n">
-        <v>6367814</v>
+        <v>6367706</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1811,11 +1811,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Skog röjd på en och små lövträd.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1824,6 +1819,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2062,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133906090</v>
+        <v>133906043</v>
       </c>
       <c r="B15" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2093,14 +2093,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716837</v>
+        <v>716740</v>
       </c>
       <c r="R15" t="n">
-        <v>6367949</v>
+        <v>6367726</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2164,10 +2164,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133906043</v>
+        <v>133906090</v>
       </c>
       <c r="B16" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2195,14 +2195,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716740</v>
+        <v>716837</v>
       </c>
       <c r="R16" t="n">
-        <v>6367726</v>
+        <v>6367949</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2269,7 +2269,7 @@
         <v>133906106</v>
       </c>
       <c r="B17" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>133906102</v>
       </c>
       <c r="B18" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2702,10 +2702,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133906092</v>
+        <v>133906001</v>
       </c>
       <c r="B21" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,14 +2733,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716848</v>
+        <v>716693</v>
       </c>
       <c r="R21" t="n">
-        <v>6367955</v>
+        <v>6367557</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2775,11 +2775,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2791,7 +2786,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2809,10 +2804,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133906001</v>
+        <v>133906092</v>
       </c>
       <c r="B22" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2840,14 +2835,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>716693</v>
+        <v>716848</v>
       </c>
       <c r="R22" t="n">
-        <v>6367557</v>
+        <v>6367955</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2882,6 +2877,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -2914,7 +2914,7 @@
         <v>133906094</v>
       </c>
       <c r="B23" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>133906078</v>
       </c>
       <c r="B24" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>133906111</v>
       </c>
       <c r="B25" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>133906096</v>
       </c>
       <c r="B26" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>133906016</v>
       </c>
       <c r="B27" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>133906116</v>
       </c>
       <c r="B28" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>133906109</v>
       </c>
       <c r="B30" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>133906034</v>
       </c>
       <c r="B31" t="n">
-        <v>110141</v>
+        <v>110142</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 63149-2025 artfynd.xlsx
+++ b/artfynd/A 63149-2025 artfynd.xlsx
@@ -2702,7 +2702,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133906001</v>
+        <v>133906092</v>
       </c>
       <c r="B21" t="n">
         <v>110142</v>
@@ -2733,14 +2733,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716693</v>
+        <v>716848</v>
       </c>
       <c r="R21" t="n">
-        <v>6367557</v>
+        <v>6367955</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2775,6 +2775,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2786,7 +2791,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2804,7 +2809,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133906092</v>
+        <v>133906001</v>
       </c>
       <c r="B22" t="n">
         <v>110142</v>
@@ -2835,14 +2840,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>716848</v>
+        <v>716693</v>
       </c>
       <c r="R22" t="n">
-        <v>6367955</v>
+        <v>6367557</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2877,11 +2882,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>

--- a/artfynd/A 63149-2025 artfynd.xlsx
+++ b/artfynd/A 63149-2025 artfynd.xlsx
@@ -1204,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133905920</v>
+        <v>133906087</v>
       </c>
       <c r="B7" t="n">
-        <v>57972</v>
+        <v>110142</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,42 +1215,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716715</v>
+        <v>716824</v>
       </c>
       <c r="R7" t="n">
-        <v>6367553</v>
+        <v>6367939</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,6 +1285,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1306,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133906087</v>
+        <v>133905920</v>
       </c>
       <c r="B8" t="n">
-        <v>110142</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1317,37 +1317,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716824</v>
+        <v>716715</v>
       </c>
       <c r="R8" t="n">
-        <v>6367939</v>
+        <v>6367553</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,11 +1392,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133905919</v>
+        <v>133906080</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>110142</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,39 +1419,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716736</v>
+        <v>716847</v>
       </c>
       <c r="R9" t="n">
-        <v>6367574</v>
+        <v>6367921</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1486,11 +1481,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosök vid basen av död gran.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1499,6 +1489,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1515,10 +1510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133906080</v>
+        <v>133905919</v>
       </c>
       <c r="B10" t="n">
-        <v>110142</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,34 +1521,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716847</v>
+        <v>716736</v>
       </c>
       <c r="R10" t="n">
-        <v>6367921</v>
+        <v>6367574</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1588,6 +1588,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födosök vid basen av död gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1596,11 +1601,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -3232,7 +3232,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133906096</v>
+        <v>133906016</v>
       </c>
       <c r="B26" t="n">
         <v>110142</v>
@@ -3263,14 +3263,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716857</v>
+        <v>716764</v>
       </c>
       <c r="R26" t="n">
-        <v>6367975</v>
+        <v>6367627</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3305,11 +3305,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3321,7 +3316,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3339,7 +3334,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133906016</v>
+        <v>133906096</v>
       </c>
       <c r="B27" t="n">
         <v>110142</v>
@@ -3370,14 +3365,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>716764</v>
+        <v>716857</v>
       </c>
       <c r="R27" t="n">
-        <v>6367627</v>
+        <v>6367975</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3412,6 +3407,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>

--- a/artfynd/A 63149-2025 artfynd.xlsx
+++ b/artfynd/A 63149-2025 artfynd.xlsx
@@ -2702,7 +2702,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133906092</v>
+        <v>133906001</v>
       </c>
       <c r="B21" t="n">
         <v>110142</v>
@@ -2733,14 +2733,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716848</v>
+        <v>716693</v>
       </c>
       <c r="R21" t="n">
-        <v>6367955</v>
+        <v>6367557</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2775,11 +2775,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2791,7 +2786,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2809,7 +2804,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133906001</v>
+        <v>133906092</v>
       </c>
       <c r="B22" t="n">
         <v>110142</v>
@@ -2840,14 +2835,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>716693</v>
+        <v>716848</v>
       </c>
       <c r="R22" t="n">
-        <v>6367557</v>
+        <v>6367955</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2882,6 +2877,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3232,7 +3232,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133906016</v>
+        <v>133906096</v>
       </c>
       <c r="B26" t="n">
         <v>110142</v>
@@ -3263,14 +3263,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716764</v>
+        <v>716857</v>
       </c>
       <c r="R26" t="n">
-        <v>6367627</v>
+        <v>6367975</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3305,6 +3305,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3316,7 +3321,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3334,7 +3339,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133906096</v>
+        <v>133906016</v>
       </c>
       <c r="B27" t="n">
         <v>110142</v>
@@ -3365,14 +3370,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>716857</v>
+        <v>716764</v>
       </c>
       <c r="R27" t="n">
-        <v>6367975</v>
+        <v>6367627</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3407,11 +3412,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>

--- a/artfynd/A 63149-2025 artfynd.xlsx
+++ b/artfynd/A 63149-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>133906074</v>
       </c>
       <c r="B3" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>133906050</v>
       </c>
       <c r="B4" t="n">
-        <v>99156</v>
+        <v>99158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>133906041</v>
       </c>
       <c r="B5" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>133906113</v>
       </c>
       <c r="B6" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133906087</v>
+        <v>133905920</v>
       </c>
       <c r="B7" t="n">
-        <v>110142</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,37 +1215,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716824</v>
+        <v>716715</v>
       </c>
       <c r="R7" t="n">
-        <v>6367939</v>
+        <v>6367553</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,11 +1290,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1306,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133905920</v>
+        <v>133906087</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>110144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1317,42 +1317,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716715</v>
+        <v>716824</v>
       </c>
       <c r="R8" t="n">
-        <v>6367553</v>
+        <v>6367939</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1392,6 +1387,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1411,7 +1411,7 @@
         <v>133906080</v>
       </c>
       <c r="B9" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>133906030</v>
       </c>
       <c r="B12" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>133906008</v>
       </c>
       <c r="B13" t="n">
-        <v>99207</v>
+        <v>99209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>133906108</v>
       </c>
       <c r="B14" t="n">
-        <v>99207</v>
+        <v>99209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>133906043</v>
       </c>
       <c r="B15" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>133906090</v>
       </c>
       <c r="B16" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>133906106</v>
       </c>
       <c r="B17" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>133906102</v>
       </c>
       <c r="B18" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>133906077</v>
       </c>
       <c r="B19" t="n">
-        <v>99207</v>
+        <v>99209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>133906072</v>
       </c>
       <c r="B20" t="n">
-        <v>99207</v>
+        <v>99209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>133906001</v>
       </c>
       <c r="B21" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>133906092</v>
       </c>
       <c r="B22" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>133906094</v>
       </c>
       <c r="B23" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>133906078</v>
       </c>
       <c r="B24" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>133906111</v>
       </c>
       <c r="B25" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3232,10 +3232,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133906096</v>
+        <v>133906016</v>
       </c>
       <c r="B26" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3263,14 +3263,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716857</v>
+        <v>716764</v>
       </c>
       <c r="R26" t="n">
-        <v>6367975</v>
+        <v>6367627</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3305,11 +3305,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3321,7 +3316,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3339,10 +3334,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133906016</v>
+        <v>133906096</v>
       </c>
       <c r="B27" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3370,14 +3365,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>716764</v>
+        <v>716857</v>
       </c>
       <c r="R27" t="n">
-        <v>6367627</v>
+        <v>6367975</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3412,6 +3407,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3444,7 +3444,7 @@
         <v>133906116</v>
       </c>
       <c r="B28" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>133906105</v>
       </c>
       <c r="B29" t="n">
-        <v>99207</v>
+        <v>99209</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>133906109</v>
       </c>
       <c r="B30" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>133906034</v>
       </c>
       <c r="B31" t="n">
-        <v>110142</v>
+        <v>110144</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 63149-2025 artfynd.xlsx
+++ b/artfynd/A 63149-2025 artfynd.xlsx
@@ -879,59 +879,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133906050</v>
+        <v>133906041</v>
       </c>
       <c r="B4" t="n">
-        <v>99159</v>
+        <v>110145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716781</v>
+        <v>716731</v>
       </c>
       <c r="R4" t="n">
-        <v>6367774</v>
+        <v>6367719</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,45 +981,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133906041</v>
+        <v>133906050</v>
       </c>
       <c r="B5" t="n">
-        <v>110145</v>
+        <v>99159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716731</v>
+        <v>716781</v>
       </c>
       <c r="R5" t="n">
-        <v>6367719</v>
+        <v>6367774</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133905920</v>
+        <v>133906087</v>
       </c>
       <c r="B7" t="n">
-        <v>57972</v>
+        <v>110145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,42 +1215,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716715</v>
+        <v>716824</v>
       </c>
       <c r="R7" t="n">
-        <v>6367553</v>
+        <v>6367939</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,6 +1285,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1306,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133906087</v>
+        <v>133905920</v>
       </c>
       <c r="B8" t="n">
-        <v>110145</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1317,37 +1317,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716824</v>
+        <v>716715</v>
       </c>
       <c r="R8" t="n">
-        <v>6367939</v>
+        <v>6367553</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1387,11 +1392,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1617,10 +1617,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133905926</v>
+        <v>133906030</v>
       </c>
       <c r="B11" t="n">
-        <v>58698</v>
+        <v>110145</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1628,56 +1628,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103055</v>
+        <v>220299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716777</v>
+        <v>716719</v>
       </c>
       <c r="R11" t="n">
-        <v>6367814</v>
+        <v>6367706</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1709,11 +1690,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Skog röjd på en och små lövträd.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1722,6 +1698,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1738,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133906030</v>
+        <v>133905926</v>
       </c>
       <c r="B12" t="n">
-        <v>110145</v>
+        <v>58698</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,37 +1730,56 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>103055</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716719</v>
+        <v>716777</v>
       </c>
       <c r="R12" t="n">
-        <v>6367706</v>
+        <v>6367814</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1811,6 +1811,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Skog röjd på en och små lövträd.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1819,11 +1824,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1951,7 +1951,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133906043</v>
+        <v>133906090</v>
       </c>
       <c r="B14" t="n">
         <v>110145</v>
@@ -1982,14 +1982,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716740</v>
+        <v>716837</v>
       </c>
       <c r="R14" t="n">
-        <v>6367726</v>
+        <v>6367949</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2053,27 +2053,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133906090</v>
+        <v>133906008</v>
       </c>
       <c r="B15" t="n">
-        <v>110145</v>
+        <v>99210</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2081,17 +2081,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716837</v>
+        <v>716736</v>
       </c>
       <c r="R15" t="n">
-        <v>6367949</v>
+        <v>6367574</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2137,7 +2146,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2155,7 +2164,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133906106</v>
+        <v>133906043</v>
       </c>
       <c r="B16" t="n">
         <v>110145</v>
@@ -2186,14 +2195,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716891</v>
+        <v>716740</v>
       </c>
       <c r="R16" t="n">
-        <v>6367995</v>
+        <v>6367726</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2228,11 +2237,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2244,7 +2248,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2262,27 +2266,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133906008</v>
+        <v>133906106</v>
       </c>
       <c r="B17" t="n">
-        <v>99210</v>
+        <v>110145</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2290,26 +2294,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716736</v>
+        <v>716891</v>
       </c>
       <c r="R17" t="n">
-        <v>6367574</v>
+        <v>6367995</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2344,6 +2339,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2373,27 +2373,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133906102</v>
+        <v>133906077</v>
       </c>
       <c r="B18" t="n">
-        <v>110145</v>
+        <v>99210</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2401,17 +2401,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716870</v>
+        <v>716854</v>
       </c>
       <c r="R18" t="n">
-        <v>6367996</v>
+        <v>6367916</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2444,11 +2453,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2480,27 +2484,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133906077</v>
+        <v>133906102</v>
       </c>
       <c r="B19" t="n">
-        <v>99210</v>
+        <v>110145</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2508,26 +2512,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716854</v>
+        <v>716870</v>
       </c>
       <c r="R19" t="n">
-        <v>6367916</v>
+        <v>6367996</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2560,6 +2555,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2911,7 +2911,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133906078</v>
+        <v>133906094</v>
       </c>
       <c r="B23" t="n">
         <v>110145</v>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>716854</v>
+        <v>716858</v>
       </c>
       <c r="R23" t="n">
-        <v>6367916</v>
+        <v>6367961</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3018,7 +3018,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133906094</v>
+        <v>133906078</v>
       </c>
       <c r="B24" t="n">
         <v>110145</v>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>716858</v>
+        <v>716854</v>
       </c>
       <c r="R24" t="n">
-        <v>6367961</v>
+        <v>6367916</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt spridd.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 63149-2025 artfynd.xlsx
+++ b/artfynd/A 63149-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>133906074</v>
       </c>
       <c r="B3" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,45 +879,59 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133906041</v>
+        <v>133906050</v>
       </c>
       <c r="B4" t="n">
-        <v>110145</v>
+        <v>99166</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716731</v>
+        <v>716781</v>
       </c>
       <c r="R4" t="n">
-        <v>6367719</v>
+        <v>6367774</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,59 +995,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133906050</v>
+        <v>133906041</v>
       </c>
       <c r="B5" t="n">
-        <v>99159</v>
+        <v>110152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716781</v>
+        <v>716731</v>
       </c>
       <c r="R5" t="n">
-        <v>6367774</v>
+        <v>6367719</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1100,7 +1100,7 @@
         <v>133906113</v>
       </c>
       <c r="B6" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>133906087</v>
       </c>
       <c r="B7" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>133906080</v>
       </c>
       <c r="B10" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>133906030</v>
       </c>
       <c r="B11" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1840,27 +1840,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133906108</v>
+        <v>133906043</v>
       </c>
       <c r="B13" t="n">
-        <v>99210</v>
+        <v>110152</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1868,26 +1868,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716880</v>
+        <v>716740</v>
       </c>
       <c r="R13" t="n">
-        <v>6367998</v>
+        <v>6367726</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1933,7 +1924,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1951,10 +1942,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133906090</v>
+        <v>133906106</v>
       </c>
       <c r="B14" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,10 +1977,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716837</v>
+        <v>716891</v>
       </c>
       <c r="R14" t="n">
-        <v>6367949</v>
+        <v>6367995</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2022,6 +2013,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,7 +2052,7 @@
         <v>133906008</v>
       </c>
       <c r="B15" t="n">
-        <v>99210</v>
+        <v>99217</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,27 +2160,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133906043</v>
+        <v>133906108</v>
       </c>
       <c r="B16" t="n">
-        <v>110145</v>
+        <v>99217</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2192,17 +2188,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716740</v>
+        <v>716880</v>
       </c>
       <c r="R16" t="n">
-        <v>6367726</v>
+        <v>6367998</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2248,7 +2253,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2266,10 +2271,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133906106</v>
+        <v>133906090</v>
       </c>
       <c r="B17" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,10 +2306,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716891</v>
+        <v>716837</v>
       </c>
       <c r="R17" t="n">
-        <v>6367995</v>
+        <v>6367949</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2337,11 +2342,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2373,27 +2373,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133906077</v>
+        <v>133906102</v>
       </c>
       <c r="B18" t="n">
-        <v>99210</v>
+        <v>110152</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2401,26 +2401,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716854</v>
+        <v>716870</v>
       </c>
       <c r="R18" t="n">
-        <v>6367916</v>
+        <v>6367996</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2453,6 +2444,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,27 +2480,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133906102</v>
+        <v>133906077</v>
       </c>
       <c r="B19" t="n">
-        <v>110145</v>
+        <v>99217</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2512,17 +2508,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716870</v>
+        <v>716854</v>
       </c>
       <c r="R19" t="n">
-        <v>6367996</v>
+        <v>6367916</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2555,11 +2560,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2594,7 +2594,7 @@
         <v>133906072</v>
       </c>
       <c r="B20" t="n">
-        <v>99210</v>
+        <v>99217</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2702,10 +2702,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133906001</v>
+        <v>133906092</v>
       </c>
       <c r="B21" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,14 +2733,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716693</v>
+        <v>716848</v>
       </c>
       <c r="R21" t="n">
-        <v>6367557</v>
+        <v>6367955</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2775,6 +2775,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2786,7 +2791,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2804,10 +2809,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133906092</v>
+        <v>133906001</v>
       </c>
       <c r="B22" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2835,14 +2840,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>716848</v>
+        <v>716693</v>
       </c>
       <c r="R22" t="n">
-        <v>6367955</v>
+        <v>6367557</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2877,11 +2882,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -2914,7 +2914,7 @@
         <v>133906094</v>
       </c>
       <c r="B23" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>133906078</v>
       </c>
       <c r="B24" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>133906111</v>
       </c>
       <c r="B25" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>133906016</v>
       </c>
       <c r="B26" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>133906096</v>
       </c>
       <c r="B27" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3441,27 +3441,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133906116</v>
+        <v>133906105</v>
       </c>
       <c r="B28" t="n">
-        <v>110145</v>
+        <v>99217</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3469,20 +3469,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>716870</v>
+        <v>716891</v>
       </c>
       <c r="R28" t="n">
-        <v>6367944</v>
+        <v>6367995</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3512,11 +3521,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Skogen buskröjd inför avverkning. Mellanskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3548,27 +3552,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133906105</v>
+        <v>133906116</v>
       </c>
       <c r="B29" t="n">
-        <v>99210</v>
+        <v>110152</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3576,29 +3580,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>716891</v>
+        <v>716870</v>
       </c>
       <c r="R29" t="n">
-        <v>6367995</v>
+        <v>6367944</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3628,6 +3623,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Skogen buskröjd inför avverkning. Mellanskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3662,7 +3662,7 @@
         <v>133906109</v>
       </c>
       <c r="B30" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>133906034</v>
       </c>
       <c r="B31" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 63149-2025 artfynd.xlsx
+++ b/artfynd/A 63149-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128721654</v>
       </c>
       <c r="B2" t="n">
-        <v>86957</v>
+        <v>87309</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,45 +772,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133906074</v>
+        <v>133905919</v>
       </c>
       <c r="B3" t="n">
-        <v>110152</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716847</v>
+        <v>716736</v>
       </c>
       <c r="R3" t="n">
-        <v>6367896</v>
+        <v>6367574</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -847,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikt spridd.</t>
+          <t>Födosök vid basen av död gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -858,11 +863,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133906050</v>
+        <v>133905920</v>
       </c>
       <c r="B4" t="n">
-        <v>99166</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,36 +890,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -928,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716781</v>
+        <v>716715</v>
       </c>
       <c r="R4" t="n">
-        <v>6367774</v>
+        <v>6367553</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,11 +965,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -995,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133906041</v>
+        <v>133905926</v>
       </c>
       <c r="B5" t="n">
-        <v>110152</v>
+        <v>58698</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,37 +992,56 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716731</v>
+        <v>716777</v>
       </c>
       <c r="R5" t="n">
-        <v>6367719</v>
+        <v>6367814</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,6 +1073,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Skog röjd på en och små lövträd.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1076,11 +1086,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1097,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133906113</v>
+        <v>134134873</v>
       </c>
       <c r="B6" t="n">
-        <v>110152</v>
+        <v>43469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,34 +1113,53 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>201116</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Berggräsfjäril</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lasiommata petropolitana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fabricius, 1787)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716867</v>
+        <v>716824</v>
       </c>
       <c r="R6" t="n">
-        <v>6367982</v>
+        <v>6367869</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1170,11 +1194,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1183,11 +1202,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1204,45 +1218,59 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133906087</v>
+        <v>133906050</v>
       </c>
       <c r="B7" t="n">
-        <v>110152</v>
+        <v>99173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716824</v>
+        <v>716781</v>
       </c>
       <c r="R7" t="n">
-        <v>6367939</v>
+        <v>6367774</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1288,7 +1316,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1306,38 +1334,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133905920</v>
+        <v>133906008</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>99224</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>219864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1346,13 +1378,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716715</v>
+        <v>716736</v>
       </c>
       <c r="R8" t="n">
-        <v>6367553</v>
+        <v>6367574</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1392,6 +1424,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1408,53 +1445,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133905919</v>
+        <v>133906069</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>99224</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>219864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg N., Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716736</v>
+        <v>716798</v>
       </c>
       <c r="R9" t="n">
-        <v>6367574</v>
+        <v>6367869</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1488,7 +1520,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Födosök vid basen av död gran.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,6 +1531,11 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kalkhällmark, alvar.</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1515,27 +1552,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133906080</v>
+        <v>133906072</v>
       </c>
       <c r="B10" t="n">
-        <v>110152</v>
+        <v>99224</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1543,17 +1580,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716847</v>
+        <v>716824</v>
       </c>
       <c r="R10" t="n">
-        <v>6367921</v>
+        <v>6367869</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1617,27 +1663,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133906030</v>
+        <v>133906077</v>
       </c>
       <c r="B11" t="n">
-        <v>110152</v>
+        <v>99224</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1645,17 +1691,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716719</v>
+        <v>716854</v>
       </c>
       <c r="R11" t="n">
-        <v>6367706</v>
+        <v>6367916</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1701,7 +1756,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1719,32 +1774,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133905926</v>
+        <v>133906105</v>
       </c>
       <c r="B12" t="n">
-        <v>58698</v>
+        <v>99224</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103055</v>
+        <v>219864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1752,34 +1807,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716777</v>
+        <v>716891</v>
       </c>
       <c r="R12" t="n">
-        <v>6367814</v>
+        <v>6367995</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1811,11 +1856,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Skog röjd på en och små lövträd.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1824,6 +1864,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1840,27 +1885,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133906043</v>
+        <v>133906108</v>
       </c>
       <c r="B13" t="n">
-        <v>110152</v>
+        <v>99224</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220299</v>
+        <v>219864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1868,17 +1913,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716740</v>
+        <v>716880</v>
       </c>
       <c r="R13" t="n">
-        <v>6367726</v>
+        <v>6367998</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1924,7 +1978,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1942,10 +1996,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133906106</v>
+        <v>133906065</v>
       </c>
       <c r="B14" t="n">
-        <v>110152</v>
+        <v>104719</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1953,37 +2007,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg N., Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716891</v>
+        <v>716798</v>
       </c>
       <c r="R14" t="n">
-        <v>6367995</v>
+        <v>6367869</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2015,11 +2069,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2031,7 +2080,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkhällmark, alvar.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2049,27 +2098,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133906008</v>
+        <v>133906001</v>
       </c>
       <c r="B15" t="n">
-        <v>99217</v>
+        <v>110159</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2077,26 +2126,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716736</v>
+        <v>716693</v>
       </c>
       <c r="R15" t="n">
-        <v>6367574</v>
+        <v>6367557</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2160,27 +2200,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133906108</v>
+        <v>133906016</v>
       </c>
       <c r="B16" t="n">
-        <v>99217</v>
+        <v>110159</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2188,26 +2228,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716880</v>
+        <v>716764</v>
       </c>
       <c r="R16" t="n">
-        <v>6367998</v>
+        <v>6367627</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2253,7 +2284,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2271,10 +2302,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133906090</v>
+        <v>133906026</v>
       </c>
       <c r="B17" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2302,14 +2333,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716837</v>
+        <v>716755</v>
       </c>
       <c r="R17" t="n">
-        <v>6367949</v>
+        <v>6367678</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2355,7 +2386,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2373,10 +2404,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133906102</v>
+        <v>133906028</v>
       </c>
       <c r="B18" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2404,14 +2435,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716870</v>
+        <v>716740</v>
       </c>
       <c r="R18" t="n">
-        <v>6367996</v>
+        <v>6367688</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2446,11 +2477,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2462,7 +2488,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2480,27 +2506,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133906077</v>
+        <v>133906030</v>
       </c>
       <c r="B19" t="n">
-        <v>99217</v>
+        <v>110159</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2508,26 +2534,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716854</v>
+        <v>716719</v>
       </c>
       <c r="R19" t="n">
-        <v>6367916</v>
+        <v>6367706</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2573,7 +2590,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2591,27 +2608,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133906072</v>
+        <v>133906034</v>
       </c>
       <c r="B20" t="n">
-        <v>99217</v>
+        <v>110159</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2619,26 +2636,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>716824</v>
+        <v>716743</v>
       </c>
       <c r="R20" t="n">
-        <v>6367869</v>
+        <v>6367714</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2684,7 +2692,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2702,10 +2710,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133906092</v>
+        <v>133906041</v>
       </c>
       <c r="B21" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,14 +2741,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716848</v>
+        <v>716731</v>
       </c>
       <c r="R21" t="n">
-        <v>6367955</v>
+        <v>6367719</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2775,11 +2783,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2791,7 +2794,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2809,10 +2812,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133906001</v>
+        <v>133906043</v>
       </c>
       <c r="B22" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,10 +2847,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>716693</v>
+        <v>716740</v>
       </c>
       <c r="R22" t="n">
-        <v>6367557</v>
+        <v>6367726</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2911,10 +2914,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133906094</v>
+        <v>133906074</v>
       </c>
       <c r="B23" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2946,10 +2949,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>716858</v>
+        <v>716847</v>
       </c>
       <c r="R23" t="n">
-        <v>6367961</v>
+        <v>6367896</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2986,7 +2989,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt spridd.</t>
+          <t>Rikt spridd.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3021,7 +3024,7 @@
         <v>133906078</v>
       </c>
       <c r="B24" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3125,10 +3128,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133906111</v>
+        <v>133906080</v>
       </c>
       <c r="B25" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3160,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>716880</v>
+        <v>716847</v>
       </c>
       <c r="R25" t="n">
-        <v>6367991</v>
+        <v>6367921</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3196,11 +3199,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3232,10 +3230,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133906016</v>
+        <v>133906082</v>
       </c>
       <c r="B26" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3263,14 +3261,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716764</v>
+        <v>716824</v>
       </c>
       <c r="R26" t="n">
-        <v>6367627</v>
+        <v>6367939</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3305,6 +3303,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikt spridd.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3316,7 +3319,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3334,10 +3337,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133906096</v>
+        <v>133906090</v>
       </c>
       <c r="B27" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3369,10 +3372,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>716857</v>
+        <v>716837</v>
       </c>
       <c r="R27" t="n">
-        <v>6367975</v>
+        <v>6367949</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3405,11 +3408,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3441,27 +3439,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133906105</v>
+        <v>133906092</v>
       </c>
       <c r="B28" t="n">
-        <v>99217</v>
+        <v>110159</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219864</v>
+        <v>220299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3469,26 +3467,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>716891</v>
+        <v>716848</v>
       </c>
       <c r="R28" t="n">
-        <v>6367995</v>
+        <v>6367955</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3521,6 +3510,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3552,10 +3546,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133906116</v>
+        <v>133906094</v>
       </c>
       <c r="B29" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3587,13 +3581,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>716870</v>
+        <v>716858</v>
       </c>
       <c r="R29" t="n">
-        <v>6367944</v>
+        <v>6367961</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3627,7 +3621,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Skogen buskröjd inför avverkning. Mellanskog.</t>
+          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3659,10 +3653,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133906109</v>
+        <v>133906096</v>
       </c>
       <c r="B30" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3694,10 +3688,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>716880</v>
+        <v>716857</v>
       </c>
       <c r="R30" t="n">
-        <v>6367998</v>
+        <v>6367975</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3766,10 +3760,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133906034</v>
+        <v>133906100</v>
       </c>
       <c r="B31" t="n">
-        <v>110152</v>
+        <v>110159</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3797,14 +3791,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>716743</v>
+        <v>716857</v>
       </c>
       <c r="R31" t="n">
-        <v>6367714</v>
+        <v>6367987</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3850,7 +3844,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3865,6 +3859,852 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133906102</v>
+      </c>
+      <c r="B32" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>716870</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6367996</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>133906106</v>
+      </c>
+      <c r="B33" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>716891</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6367995</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>133906109</v>
+      </c>
+      <c r="B34" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>716880</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6367998</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>133906111</v>
+      </c>
+      <c r="B35" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>716880</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6367991</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>133906113</v>
+      </c>
+      <c r="B36" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>716867</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6367982</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>133906116</v>
+      </c>
+      <c r="B37" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>716870</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6367944</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Skogen buskröjd inför avverkning. Mellanskog.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>133906064</v>
+      </c>
+      <c r="B38" t="n">
+        <v>107598</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26, körväg N., Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>716798</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6367869</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkhällmark, alvar.</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>133906012</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>716740</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6367716</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63149-2025 artfynd.xlsx
+++ b/artfynd/A 63149-2025 artfynd.xlsx
@@ -3831,12 +3831,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3943,12 +3943,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4055,12 +4055,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4167,12 +4167,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4279,12 +4279,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4391,12 +4391,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4503,12 +4503,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4615,12 +4615,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4727,12 +4727,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4839,12 +4839,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4951,12 +4951,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5063,12 +5063,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5175,12 +5175,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5287,12 +5287,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5399,12 +5399,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5511,12 +5511,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5623,12 +5623,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5735,12 +5735,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5847,12 +5847,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5959,12 +5959,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6071,12 +6071,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6183,12 +6183,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6295,12 +6295,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6407,12 +6407,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6519,12 +6519,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6631,12 +6631,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6743,12 +6743,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6855,12 +6855,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6967,12 +6967,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7079,12 +7079,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7191,12 +7191,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7303,12 +7303,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7415,12 +7415,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7527,12 +7527,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7639,12 +7639,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7751,12 +7751,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7863,12 +7863,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>

--- a/artfynd/A 63149-2025 artfynd.xlsx
+++ b/artfynd/A 63149-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY103"/>
+  <dimension ref="A1:AZ103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721654</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133905919</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133905920</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649762</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649764</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649768</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1416,6 +1451,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649770</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649774</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649775</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1752,6 +1802,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649779</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1864,6 +1919,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649781</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1971,6 +2031,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649783</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2078,6 +2143,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649786</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2185,6 +2255,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649788</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2297,6 +2372,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649791</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2404,6 +2484,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649793</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2511,6 +2596,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649797</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2623,6 +2713,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649799</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2735,6 +2830,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649803</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2847,6 +2947,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649805</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2959,6 +3064,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649809</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3071,6 +3181,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649811</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3183,6 +3298,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649813</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3290,6 +3410,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649816</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3397,6 +3522,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649818</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3509,6 +3639,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649820</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3616,6 +3751,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649822</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3728,6 +3868,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649826</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3840,6 +3985,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658143</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3952,6 +4102,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658147</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4064,6 +4219,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658148</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4176,6 +4336,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658149</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4288,6 +4453,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658150</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4400,6 +4570,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658154</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4512,6 +4687,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658155</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4624,6 +4804,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658157</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4736,6 +4921,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658158</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4848,6 +5038,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658160</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4960,6 +5155,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658163</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5072,6 +5272,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658165</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5184,6 +5389,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658168</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5296,6 +5506,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658169</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5408,6 +5623,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658171</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5520,6 +5740,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658175</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5632,6 +5857,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658176</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5744,6 +5974,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658179</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5856,6 +6091,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658180</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5968,6 +6208,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658181</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6080,6 +6325,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658183</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6192,6 +6442,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658184</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6304,6 +6559,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658185</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6416,6 +6676,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658186</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6528,6 +6793,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658187</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6640,6 +6910,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658189</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6752,6 +7027,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658190</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6864,6 +7144,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658191</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6976,6 +7261,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658192</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7088,6 +7378,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658193</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7200,6 +7495,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658195</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7312,6 +7612,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658196</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7424,6 +7729,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658198</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7536,6 +7846,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658199</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7648,6 +7963,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658200</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7760,6 +8080,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658202</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7872,6 +8197,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134658204</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7993,6 +8323,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133905926</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8109,6 +8444,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134134873</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8225,6 +8565,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906050</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8336,6 +8681,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906008</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8443,6 +8793,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906069</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8554,6 +8909,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906072</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8665,6 +9025,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906077</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8776,6 +9141,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906105</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8887,6 +9257,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906108</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8994,6 +9369,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649830</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9096,6 +9476,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906065</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9198,6 +9583,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906001</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9300,6 +9690,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906016</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9402,6 +9797,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906026</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9504,6 +9904,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906028</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9606,6 +10011,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906030</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9708,6 +10118,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906034</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9810,6 +10225,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906041</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9912,6 +10332,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906043</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10019,6 +10444,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906074</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10126,6 +10556,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906078</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10228,6 +10663,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906080</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10335,6 +10775,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906082</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10437,6 +10882,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906090</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10544,6 +10994,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906092</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10651,6 +11106,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906094</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10758,6 +11218,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906096</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10860,6 +11325,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906100</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10967,6 +11437,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906102</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11074,6 +11549,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906106</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11181,6 +11661,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906109</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11288,6 +11773,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906111</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11395,6 +11885,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906113</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11502,6 +11997,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906116</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11604,6 +12104,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906064</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11706,6 +12211,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906012</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11813,8 +12323,117 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134649829</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>